--- a/PD_LTSF_Auto_Bulk_US.xlsx
+++ b/PD_LTSF_Auto_Bulk_US.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="4">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="47">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="AB82" t="n">
-        <v>0.65</v>
+        <v>0.41</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="AB83" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="AB84" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
